--- a/Project-15 ---/Data/data.xlsx
+++ b/Project-15 ---/Data/data.xlsx
@@ -1,15 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F6B982-F095-4541-B38D-209BFDFC0291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="9765" yWindow="60" windowWidth="17250" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AT$1</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -179,8 +183,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,13 +221,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -261,7 +273,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -295,6 +307,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -329,9 +342,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -504,9 +518,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AT112"/>
-  <sheetFormatPr defaultColWidth="4" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="4" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.42578125" bestFit="1" customWidth="1"/>
@@ -555,7 +569,7 @@
     <col min="46" max="46" width="31.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>48</v>
       </c>
@@ -695,7 +709,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:46">
+    <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -760,7 +774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:46">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -825,7 +839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:46">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -890,7 +904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:46">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -955,7 +969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:46">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1023,7 +1037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:46">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1088,7 +1102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:46">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1138,7 +1152,7 @@
         <v>1</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>0.3</v>
@@ -1156,7 +1170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:46">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1218,7 +1232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:46">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1283,7 +1297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:46">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1333,7 +1347,7 @@
         <v>2</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1348,7 +1362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:46">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1410,7 +1424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:46">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1481,7 +1495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:46">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1546,7 +1560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:46">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1608,7 +1622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:46">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1673,7 +1687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:44">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1738,7 +1752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:44">
+    <row r="18" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1803,7 +1817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:44">
+    <row r="19" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1865,7 +1879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:44">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1933,7 +1947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:44">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1983,7 +1997,7 @@
         <v>1</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21">
         <v>0.3</v>
@@ -2001,7 +2015,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:44">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2063,7 +2077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:44">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2125,7 +2139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:44">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2187,7 +2201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:44">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2249,7 +2263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:44">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2311,7 +2325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:44">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2382,7 +2396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:44">
+    <row r="28" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2444,7 +2458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:44">
+    <row r="29" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2494,7 +2508,7 @@
         <v>2</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>0.6</v>
@@ -2512,7 +2526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:44">
+    <row r="30" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2577,7 +2591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:44">
+    <row r="31" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2642,7 +2656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:44">
+    <row r="32" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2707,7 +2721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:45">
+    <row r="33" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2757,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -2772,7 +2786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:45">
+    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2837,7 +2851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:45">
+    <row r="35" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2899,7 +2913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:45">
+    <row r="36" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2964,7 +2978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:45">
+    <row r="37" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3041,7 +3055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:45">
+    <row r="38" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3106,7 +3120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:45">
+    <row r="39" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3168,7 +3182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:45">
+    <row r="40" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3230,7 +3244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:45">
+    <row r="41" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3292,7 +3306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:45">
+    <row r="42" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3341,6 +3355,9 @@
       <c r="P42">
         <v>1</v>
       </c>
+      <c r="Q42">
+        <v>2</v>
+      </c>
       <c r="R42">
         <v>0</v>
       </c>
@@ -3351,7 +3368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:45">
+    <row r="43" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3398,7 +3415,7 @@
         <v>52</v>
       </c>
       <c r="P43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q43">
         <v>2</v>
@@ -3416,7 +3433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:45">
+    <row r="44" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3481,7 +3498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:45">
+    <row r="45" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3540,7 +3557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:45">
+    <row r="46" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3602,7 +3619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:45">
+    <row r="47" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3664,7 +3681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:45">
+    <row r="48" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3726,7 +3743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:43">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3791,7 +3808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:43">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3862,7 +3879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:43">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3930,7 +3947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:43">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3995,7 +4012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:43">
+    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4060,7 +4077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:43">
+    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4122,7 +4139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:43">
+    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4172,7 +4189,7 @@
         <v>1</v>
       </c>
       <c r="Q55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R55">
         <v>0.17</v>
@@ -4193,7 +4210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:43">
+    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4258,7 +4275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:43">
+    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4323,7 +4340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:43">
+    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4394,7 +4411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:43">
+    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4459,7 +4476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:43">
+    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4530,7 +4547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:43">
+    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4598,7 +4615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:43">
+    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4666,7 +4683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:43">
+    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4713,7 +4730,7 @@
         <v>52</v>
       </c>
       <c r="P63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q63">
         <v>2</v>
@@ -4740,7 +4757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:43">
+    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4802,7 +4819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:46">
+    <row r="65" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4873,7 +4890,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:46">
+    <row r="66" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4938,7 +4955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:46">
+    <row r="67" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5003,7 +5020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:46">
+    <row r="68" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5068,7 +5085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:46">
+    <row r="69" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5133,7 +5150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:46">
+    <row r="70" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5198,7 +5215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:46">
+    <row r="71" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5263,7 +5280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:46">
+    <row r="72" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5331,7 +5348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:46">
+    <row r="73" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5396,7 +5413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:46">
+    <row r="74" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5461,7 +5478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:46">
+    <row r="75" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5526,7 +5543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:46">
+    <row r="76" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5591,7 +5608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:46">
+    <row r="77" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5653,7 +5670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:46">
+    <row r="78" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5721,7 +5738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:46">
+    <row r="79" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5786,7 +5803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:46">
+    <row r="80" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5851,7 +5868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:44">
+    <row r="81" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5919,7 +5936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:44">
+    <row r="82" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5981,7 +5998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:44">
+    <row r="83" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6046,7 +6063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:44">
+    <row r="84" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6111,7 +6128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:44">
+    <row r="85" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6182,7 +6199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:44">
+    <row r="86" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6244,7 +6261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:44">
+    <row r="87" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6306,7 +6323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:44">
+    <row r="88" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6368,7 +6385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:44">
+    <row r="89" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6430,7 +6447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:44">
+    <row r="90" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6498,7 +6515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:44">
+    <row r="91" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6563,7 +6580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:44">
+    <row r="92" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -6628,7 +6645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:44">
+    <row r="93" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -6693,7 +6710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:44">
+    <row r="94" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -6743,7 +6760,7 @@
         <v>1</v>
       </c>
       <c r="Q94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -6758,7 +6775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:44">
+    <row r="95" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -6820,7 +6837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:44">
+    <row r="96" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6882,7 +6899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:42">
+    <row r="97" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -6931,6 +6948,9 @@
       <c r="P97">
         <v>1</v>
       </c>
+      <c r="Q97">
+        <v>1</v>
+      </c>
       <c r="R97">
         <v>0</v>
       </c>
@@ -6941,7 +6961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:42">
+    <row r="98" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7006,7 +7026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:42">
+    <row r="99" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7068,7 +7088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:42">
+    <row r="100" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7136,7 +7156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:42">
+    <row r="101" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7198,7 +7218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:42">
+    <row r="102" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -7269,7 +7289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:42">
+    <row r="103" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -7319,7 +7339,7 @@
         <v>1</v>
       </c>
       <c r="Q103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R103">
         <v>0.6</v>
@@ -7340,7 +7360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:42">
+    <row r="104" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -7408,7 +7428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:42">
+    <row r="105" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -7476,7 +7496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:42">
+    <row r="106" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -7541,7 +7561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:42">
+    <row r="107" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -7606,7 +7626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:42">
+    <row r="108" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -7671,7 +7691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:42">
+    <row r="109" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -7736,7 +7756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:42">
+    <row r="110" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -7786,7 +7806,7 @@
         <v>1</v>
       </c>
       <c r="Q110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -7801,7 +7821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:42">
+    <row r="111" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -7866,7 +7886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:42">
+    <row r="112" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -7932,14 +7952,15 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AT1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.7109375" bestFit="1" customWidth="1"/>
